--- a/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/01_PPC1 - Kontrol Planı, Muayene ve Serbest Bırakma/EKG-KLT-FRM-25_final_kontrol_raporu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/04_Parça ve Proses Kontrolü/01_PPC1 - Kontrol Planı, Muayene ve Serbest Bırakma/EKG-KLT-FRM-25_final_kontrol_raporu.xlsx
@@ -2609,7 +2609,7 @@
       <c r="H2" s="77"/>
       <c r="I2" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">04.05.2026</t>
+          <t xml:space="preserve">10.06.2026</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       <c r="H4" s="77"/>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">19.10.2026</t>
+          <t xml:space="preserve">18.09.2026</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,8 @@
   <pageSetup paperSize="9" scale="67" orientation="portrait" r:id="rId1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-25&amp;C&amp;"Arial,Regular"&amp;11Final Kontrol Raporu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 18.09.2026
+Revizyon nedeni: Lot/numune izi ve yetkili serbest bırakma alanları eklendi; şartlı kabul müşteri iznine bağlandı.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
